--- a/MotorDriver/bom/MotorDriver.xlsx
+++ b/MotorDriver/bom/MotorDriver.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\Robocon2025-PCB\MotorDriver\bom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\MyFiles\ロボット研究部\基板\Robocon2025-PCB\MotorDriver\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FF8D37DB-9852-40A2-84AD-ED1EF24522B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04508E16-1FD4-4F96-80F4-F3E12E249FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-210" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{7E4276CA-38E8-4AFB-B519-20FC74FB4699}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7E4276CA-38E8-4AFB-B519-20FC74FB4699}"/>
   </bookViews>
   <sheets>
     <sheet name="MotorDriver" sheetId="1" r:id="rId1"/>
+    <sheet name="印刷用" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="234">
   <si>
     <t>Reference</t>
   </si>
@@ -734,11 +748,18 @@
     <t>*</t>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>R19,R20,R24,R25,R30,R39,R40</t>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_ "/>
+  </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1325,7 +1346,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1334,6 +1355,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -3216,4 +3246,1519 @@
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1056104B-5A35-4850-AFDB-E80B57EB79AB}">
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="8" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>37</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <f>E2*F2</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>27</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G60" si="0">E3*F3</f>
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>34</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>408</v>
+      </c>
+      <c r="H4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3">
+        <v>885012006029</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10">
+        <v>44</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11">
+        <v>29</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="H11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12">
+        <v>47</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>329</v>
+      </c>
+      <c r="H12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>29</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <v>29</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15">
+        <v>15</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16">
+        <v>52</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>156</v>
+      </c>
+      <c r="H16" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19">
+        <v>62</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20">
+        <v>116</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21">
+        <v>84</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22">
+        <v>100</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24">
+        <v>76</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="H24" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25">
+        <v>110</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26">
+        <v>442</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>884</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="1">
+        <v>420430</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28">
+        <v>22</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29">
+        <v>120</v>
+      </c>
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29">
+        <v>22</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30">
+        <v>22</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31">
+        <v>600</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31">
+        <v>22</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32">
+        <v>300</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32">
+        <v>22</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33">
+        <v>330</v>
+      </c>
+      <c r="C33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33">
+        <v>22</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34">
+        <v>22</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35">
+        <v>22</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36">
+        <v>15</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37">
+        <v>18</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39">
+        <v>15</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" t="s">
+        <v>151</v>
+      </c>
+      <c r="E40">
+        <v>22</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41">
+        <v>15</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42">
+        <v>22</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>161</v>
+      </c>
+      <c r="B43" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43">
+        <v>22</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44">
+        <v>350</v>
+      </c>
+      <c r="C44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" t="s">
+        <v>166</v>
+      </c>
+      <c r="E44">
+        <v>15</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>168</v>
+      </c>
+      <c r="B45">
+        <v>660</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" t="s">
+        <v>169</v>
+      </c>
+      <c r="E45">
+        <v>15</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46">
+        <v>233</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="0"/>
+        <v>466</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47">
+        <v>87</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>178</v>
+      </c>
+      <c r="B48" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" t="s">
+        <v>180</v>
+      </c>
+      <c r="E48">
+        <v>458</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" t="s">
+        <v>183</v>
+      </c>
+      <c r="C49" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49">
+        <v>22</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" t="s">
+        <v>187</v>
+      </c>
+      <c r="C50" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50">
+        <v>244</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C51" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" t="s">
+        <v>192</v>
+      </c>
+      <c r="E51">
+        <v>50</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" t="s">
+        <v>194</v>
+      </c>
+      <c r="C52" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" t="s">
+        <v>195</v>
+      </c>
+      <c r="E52">
+        <v>63</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" t="s">
+        <v>198</v>
+      </c>
+      <c r="C53" t="s">
+        <v>200</v>
+      </c>
+      <c r="D53" t="s">
+        <v>199</v>
+      </c>
+      <c r="E53">
+        <v>897</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="0"/>
+        <v>897</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" t="s">
+        <v>202</v>
+      </c>
+      <c r="C54" t="s">
+        <v>204</v>
+      </c>
+      <c r="D54" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54">
+        <v>260</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" t="s">
+        <v>208</v>
+      </c>
+      <c r="D55" t="s">
+        <v>207</v>
+      </c>
+      <c r="E55">
+        <v>24</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" t="s">
+        <v>212</v>
+      </c>
+      <c r="D56" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56">
+        <v>780</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>213</v>
+      </c>
+      <c r="B57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" t="s">
+        <v>216</v>
+      </c>
+      <c r="D57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E57">
+        <v>202</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="0"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>217</v>
+      </c>
+      <c r="B58" t="s">
+        <v>218</v>
+      </c>
+      <c r="C58" t="s">
+        <v>218</v>
+      </c>
+      <c r="D58" t="s">
+        <v>219</v>
+      </c>
+      <c r="E58">
+        <v>90</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" t="s">
+        <v>223</v>
+      </c>
+      <c r="D59" t="s">
+        <v>222</v>
+      </c>
+      <c r="E59">
+        <v>80</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" t="s">
+        <v>225</v>
+      </c>
+      <c r="C60" t="s">
+        <v>227</v>
+      </c>
+      <c r="D60" t="s">
+        <v>226</v>
+      </c>
+      <c r="E60">
+        <v>52</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F62" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G62">
+        <f>SUM(G2:G60)</f>
+        <v>8135</v>
+      </c>
+      <c r="H62" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F63" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G63">
+        <f>G62-G56-G53-G23-G22</f>
+        <v>6258</v>
+      </c>
+      <c r="H63" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.15748031496062992" header="0.31496062992125984" footer="0"/>
+  <pageSetup paperSize="9" scale="70" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>